--- a/docs/downloads/13/tbl_repondant_marovoay_maroala.xlsx
+++ b/docs/downloads/13/tbl_repondant_marovoay_maroala.xlsx
@@ -397,9 +397,6 @@
           <t>Autre membre</t>
         </is>
       </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -457,9 +454,6 @@
           <t>Autre membre</t>
         </is>
       </c>
-      <c r="C7">
-        <v>3</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -487,9 +481,6 @@
           <t>Code 10</t>
         </is>
       </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -501,9 +492,6 @@
         <is>
           <t>Code NA</t>
         </is>
-      </c>
-      <c r="C10">
-        <v>2</v>
       </c>
     </row>
     <row r="11">
